--- a/artfynd/A 52245-2025 artfynd.xlsx
+++ b/artfynd/A 52245-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,6 +884,297 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129831806</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91366</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Buttle Altajme, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>713742</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6366769</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129831808</v>
+      </c>
+      <c r="B5" t="n">
+        <v>86846</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Buttle Altajme, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>713729</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6366834</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129831815</v>
+      </c>
+      <c r="B6" t="n">
+        <v>107692</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Buttle Altajme, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>713709</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6366906</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52245-2025 artfynd.xlsx
+++ b/artfynd/A 52245-2025 artfynd.xlsx
@@ -984,32 +984,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129831808</v>
+        <v>129831815</v>
       </c>
       <c r="B5" t="n">
-        <v>86846</v>
+        <v>107692</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>220079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713729</v>
+        <v>713709</v>
       </c>
       <c r="R5" t="n">
-        <v>6366834</v>
+        <v>6366906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,32 +1081,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129831815</v>
+        <v>129831808</v>
       </c>
       <c r="B6" t="n">
-        <v>107692</v>
+        <v>86846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220079</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713709</v>
+        <v>713729</v>
       </c>
       <c r="R6" t="n">
-        <v>6366906</v>
+        <v>6366834</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 52245-2025 artfynd.xlsx
+++ b/artfynd/A 52245-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>129831806</v>
       </c>
       <c r="B4" t="n">
-        <v>91366</v>
+        <v>91370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,32 +984,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129831815</v>
+        <v>129831808</v>
       </c>
       <c r="B5" t="n">
-        <v>107692</v>
+        <v>86850</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220079</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713709</v>
+        <v>713729</v>
       </c>
       <c r="R5" t="n">
-        <v>6366906</v>
+        <v>6366834</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,32 +1081,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129831808</v>
+        <v>129831815</v>
       </c>
       <c r="B6" t="n">
-        <v>86846</v>
+        <v>107696</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>220079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713729</v>
+        <v>713709</v>
       </c>
       <c r="R6" t="n">
-        <v>6366834</v>
+        <v>6366906</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 52245-2025 artfynd.xlsx
+++ b/artfynd/A 52245-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>129831806</v>
       </c>
       <c r="B4" t="n">
-        <v>91370</v>
+        <v>91372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129831808</v>
       </c>
       <c r="B5" t="n">
-        <v>86850</v>
+        <v>86852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129831815</v>
       </c>
       <c r="B6" t="n">
-        <v>107696</v>
+        <v>107698</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 52245-2025 artfynd.xlsx
+++ b/artfynd/A 52245-2025 artfynd.xlsx
@@ -1084,7 +1084,7 @@
         <v>129831815</v>
       </c>
       <c r="B6" t="n">
-        <v>107698</v>
+        <v>107708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 52245-2025 artfynd.xlsx
+++ b/artfynd/A 52245-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>129831806</v>
       </c>
       <c r="B4" t="n">
-        <v>91372</v>
+        <v>91375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129831808</v>
       </c>
       <c r="B5" t="n">
-        <v>86852</v>
+        <v>86855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129831815</v>
       </c>
       <c r="B6" t="n">
-        <v>107708</v>
+        <v>107712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 52245-2025 artfynd.xlsx
+++ b/artfynd/A 52245-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>129831806</v>
       </c>
       <c r="B4" t="n">
-        <v>91375</v>
+        <v>91378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,32 +984,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129831808</v>
+        <v>129831815</v>
       </c>
       <c r="B5" t="n">
-        <v>86855</v>
+        <v>107715</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>220079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713729</v>
+        <v>713709</v>
       </c>
       <c r="R5" t="n">
-        <v>6366834</v>
+        <v>6366906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,32 +1081,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129831815</v>
+        <v>129831808</v>
       </c>
       <c r="B6" t="n">
-        <v>107712</v>
+        <v>86858</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220079</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713709</v>
+        <v>713729</v>
       </c>
       <c r="R6" t="n">
-        <v>6366906</v>
+        <v>6366834</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 52245-2025 artfynd.xlsx
+++ b/artfynd/A 52245-2025 artfynd.xlsx
@@ -984,32 +984,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129831815</v>
+        <v>129831808</v>
       </c>
       <c r="B5" t="n">
-        <v>107715</v>
+        <v>86858</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220079</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713709</v>
+        <v>713729</v>
       </c>
       <c r="R5" t="n">
-        <v>6366906</v>
+        <v>6366834</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,32 +1081,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129831808</v>
+        <v>129831815</v>
       </c>
       <c r="B6" t="n">
-        <v>86858</v>
+        <v>107715</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>220079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713729</v>
+        <v>713709</v>
       </c>
       <c r="R6" t="n">
-        <v>6366834</v>
+        <v>6366906</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 52245-2025 artfynd.xlsx
+++ b/artfynd/A 52245-2025 artfynd.xlsx
@@ -984,32 +984,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129831808</v>
+        <v>129831815</v>
       </c>
       <c r="B5" t="n">
-        <v>86858</v>
+        <v>107715</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>220079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713729</v>
+        <v>713709</v>
       </c>
       <c r="R5" t="n">
-        <v>6366834</v>
+        <v>6366906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,32 +1081,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129831815</v>
+        <v>129831808</v>
       </c>
       <c r="B6" t="n">
-        <v>107715</v>
+        <v>86858</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220079</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713709</v>
+        <v>713729</v>
       </c>
       <c r="R6" t="n">
-        <v>6366906</v>
+        <v>6366834</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 52245-2025 artfynd.xlsx
+++ b/artfynd/A 52245-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>129831806</v>
       </c>
       <c r="B4" t="n">
-        <v>91378</v>
+        <v>91379</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129831815</v>
       </c>
       <c r="B5" t="n">
-        <v>107715</v>
+        <v>107716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129831808</v>
       </c>
       <c r="B6" t="n">
-        <v>86858</v>
+        <v>86859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 52245-2025 artfynd.xlsx
+++ b/artfynd/A 52245-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>129831806</v>
       </c>
       <c r="B4" t="n">
-        <v>91379</v>
+        <v>91396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,32 +984,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129831815</v>
+        <v>129831808</v>
       </c>
       <c r="B5" t="n">
-        <v>107716</v>
+        <v>86876</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220079</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713709</v>
+        <v>713729</v>
       </c>
       <c r="R5" t="n">
-        <v>6366906</v>
+        <v>6366834</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,32 +1081,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129831808</v>
+        <v>129831815</v>
       </c>
       <c r="B6" t="n">
-        <v>86859</v>
+        <v>107733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>220079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713729</v>
+        <v>713709</v>
       </c>
       <c r="R6" t="n">
-        <v>6366834</v>
+        <v>6366906</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 52245-2025 artfynd.xlsx
+++ b/artfynd/A 52245-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>129831806</v>
       </c>
       <c r="B4" t="n">
-        <v>91412</v>
+        <v>91414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129831815</v>
       </c>
       <c r="B6" t="n">
-        <v>107749</v>
+        <v>107752</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 52245-2025 artfynd.xlsx
+++ b/artfynd/A 52245-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>129831806</v>
       </c>
       <c r="B4" t="n">
-        <v>91414</v>
+        <v>91501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,32 +984,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129831808</v>
+        <v>129831815</v>
       </c>
       <c r="B5" t="n">
-        <v>86892</v>
+        <v>107839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>220079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713729</v>
+        <v>713709</v>
       </c>
       <c r="R5" t="n">
-        <v>6366834</v>
+        <v>6366906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,32 +1081,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129831815</v>
+        <v>129831808</v>
       </c>
       <c r="B6" t="n">
-        <v>107752</v>
+        <v>86979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220079</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713709</v>
+        <v>713729</v>
       </c>
       <c r="R6" t="n">
-        <v>6366906</v>
+        <v>6366834</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
